--- a/excepciones.xlsx
+++ b/excepciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,36 @@
       </c>
       <c r="F5" s="2" t="n">
         <v>46003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16357580</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Roberto Laforcada</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Merca</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Roberto Laforcada (hijo)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>46005</v>
       </c>
     </row>
   </sheetData>
